--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/151.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/151.xlsx
@@ -426,13 +426,13 @@
         <v>-11.88241088144541</v>
       </c>
       <c r="E2">
-        <v>-15.44212108523356</v>
+        <v>-19.96829009963401</v>
       </c>
       <c r="F2">
-        <v>-5.683277306620203</v>
+        <v>-7.127296061038031</v>
       </c>
       <c r="G2">
-        <v>-11.69286816845044</v>
+        <v>-12.89581321046627</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.73848324352061</v>
       </c>
       <c r="E3">
-        <v>-15.38124028067444</v>
+        <v>-20.08857542622575</v>
       </c>
       <c r="F3">
-        <v>-5.9521289174032</v>
+        <v>-6.930369520921609</v>
       </c>
       <c r="G3">
-        <v>-12.00268767053633</v>
+        <v>-13.79220684706941</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.56203653151766</v>
       </c>
       <c r="E4">
-        <v>-16.63198668769696</v>
+        <v>-21.31671116252798</v>
       </c>
       <c r="F4">
-        <v>-5.609159961622121</v>
+        <v>-6.870692276489127</v>
       </c>
       <c r="G4">
-        <v>-11.6931142600674</v>
+        <v>-15.30563911975847</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.37830611249944</v>
       </c>
       <c r="E5">
-        <v>-16.47328178762415</v>
+        <v>-21.61042345819147</v>
       </c>
       <c r="F5">
-        <v>-5.571505692960466</v>
+        <v>-6.609274434778853</v>
       </c>
       <c r="G5">
-        <v>-11.58707830415238</v>
+        <v>-13.32613557432276</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.1700700385491</v>
       </c>
       <c r="E6">
-        <v>-17.8119530459796</v>
+        <v>-23.51672081951236</v>
       </c>
       <c r="F6">
-        <v>-5.747759081988923</v>
+        <v>-6.873560912805021</v>
       </c>
       <c r="G6">
-        <v>-11.84009657982273</v>
+        <v>-13.84000932335818</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.94147708558213</v>
       </c>
       <c r="E7">
-        <v>-17.41936152035862</v>
+        <v>-23.1828771871929</v>
       </c>
       <c r="F7">
-        <v>-5.719051181277503</v>
+        <v>-6.730248796099992</v>
       </c>
       <c r="G7">
-        <v>-11.8802849814828</v>
+        <v>-13.87672783321914</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.68360683702498</v>
       </c>
       <c r="E8">
-        <v>-19.07434668814984</v>
+        <v>-24.70313119630791</v>
       </c>
       <c r="F8">
-        <v>-5.428923782121004</v>
+        <v>-6.987308596904137</v>
       </c>
       <c r="G8">
-        <v>-11.33219629463628</v>
+        <v>-14.40120977155625</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.38999688488655</v>
       </c>
       <c r="E9">
-        <v>-20.03148948288506</v>
+        <v>-24.85111266993057</v>
       </c>
       <c r="F9">
-        <v>-5.384468617082366</v>
+        <v>-6.988247965538911</v>
       </c>
       <c r="G9">
-        <v>-11.19269516003649</v>
+        <v>-13.51630205102194</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.05876729078784</v>
       </c>
       <c r="E10">
-        <v>-20.06414430895437</v>
+        <v>-25.41197776120256</v>
       </c>
       <c r="F10">
-        <v>-5.482809081673112</v>
+        <v>-6.744119394076168</v>
       </c>
       <c r="G10">
-        <v>-11.41942428857256</v>
+        <v>-12.98151215515584</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.678221475560077</v>
       </c>
       <c r="E11">
-        <v>-20.79183838266894</v>
+        <v>-26.35765445975036</v>
       </c>
       <c r="F11">
-        <v>-5.406668863477393</v>
+        <v>-7.018031501322866</v>
       </c>
       <c r="G11">
-        <v>-10.68414847420283</v>
+        <v>-13.21124688264036</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.259763825177499</v>
       </c>
       <c r="E12">
-        <v>-22.28582271406546</v>
+        <v>-26.79541298512384</v>
       </c>
       <c r="F12">
-        <v>-5.450154010287353</v>
+        <v>-6.994603614436891</v>
       </c>
       <c r="G12">
-        <v>-10.79735061800367</v>
+        <v>-13.56088728957167</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.797554093770627</v>
       </c>
       <c r="E13">
-        <v>-21.91755362233969</v>
+        <v>-25.89978498130882</v>
       </c>
       <c r="F13">
-        <v>-5.215166887298203</v>
+        <v>-5.809604163914531</v>
       </c>
       <c r="G13">
-        <v>-10.35062542757151</v>
+        <v>-12.1469072017386</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.320263980023633</v>
       </c>
       <c r="E14">
-        <v>-23.09705354779953</v>
+        <v>-27.6014451306971</v>
       </c>
       <c r="F14">
-        <v>-5.116422179414891</v>
+        <v>-5.374334370276516</v>
       </c>
       <c r="G14">
-        <v>-9.233139801071422</v>
+        <v>-11.87567814641334</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.842976813303438</v>
       </c>
       <c r="E15">
-        <v>-23.60834543410956</v>
+        <v>-28.18042864647378</v>
       </c>
       <c r="F15">
-        <v>-4.781644120512693</v>
+        <v>-5.272968707930747</v>
       </c>
       <c r="G15">
-        <v>-8.565991989940445</v>
+        <v>-12.12558582404533</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.401421029891056</v>
       </c>
       <c r="E16">
-        <v>-24.23405374469739</v>
+        <v>-29.04044020221848</v>
       </c>
       <c r="F16">
-        <v>-4.622700296733135</v>
+        <v>-5.955593149881707</v>
       </c>
       <c r="G16">
-        <v>-8.976728742308616</v>
+        <v>-11.10377405577553</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.021771023669311</v>
       </c>
       <c r="E17">
-        <v>-26.06877404585305</v>
+        <v>-30.71137691970172</v>
       </c>
       <c r="F17">
-        <v>-4.299142474301856</v>
+        <v>-5.688364310840795</v>
       </c>
       <c r="G17">
-        <v>-7.908025036732793</v>
+        <v>-11.05805351456623</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.726170649418184</v>
       </c>
       <c r="E18">
-        <v>-26.40115950954205</v>
+        <v>-30.66834509544383</v>
       </c>
       <c r="F18">
-        <v>-4.139188870658286</v>
+        <v>-5.606445401643146</v>
       </c>
       <c r="G18">
-        <v>-7.651029920532404</v>
+        <v>-11.10458779872228</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.535089565567415</v>
       </c>
       <c r="E19">
-        <v>-27.37298361701013</v>
+        <v>-31.42966082442835</v>
       </c>
       <c r="F19">
-        <v>-3.853262122601383</v>
+        <v>-5.437081544303774</v>
       </c>
       <c r="G19">
-        <v>-8.01918954194522</v>
+        <v>-10.54857824303125</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.446222438956365</v>
       </c>
       <c r="E20">
-        <v>-27.73000850777486</v>
+        <v>-32.0624041193871</v>
       </c>
       <c r="F20">
-        <v>-3.654613820838242</v>
+        <v>-5.085292960785088</v>
       </c>
       <c r="G20">
-        <v>-8.23623250443781</v>
+        <v>-10.86078319319085</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.467249446491881</v>
       </c>
       <c r="E21">
-        <v>-27.93965874043397</v>
+        <v>-33.05383199083438</v>
       </c>
       <c r="F21">
-        <v>-3.190792687927937</v>
+        <v>-4.671553264313236</v>
       </c>
       <c r="G21">
-        <v>-7.655331601996837</v>
+        <v>-10.55959330380631</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.573604996258101</v>
       </c>
       <c r="E22">
-        <v>-28.06945839091582</v>
+        <v>-32.9111420390897</v>
       </c>
       <c r="F22">
-        <v>-3.057745285894698</v>
+        <v>-4.487073358607577</v>
       </c>
       <c r="G22">
-        <v>-7.292690995247007</v>
+        <v>-9.991331666812313</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.758092000404035</v>
       </c>
       <c r="E23">
-        <v>-29.22680049305614</v>
+        <v>-34.64340561582181</v>
       </c>
       <c r="F23">
-        <v>-2.89754979896951</v>
+        <v>-4.66095264665961</v>
       </c>
       <c r="G23">
-        <v>-7.314865490545734</v>
+        <v>-9.92611738831835</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.990377697155885</v>
       </c>
       <c r="E24">
-        <v>-29.6577617789441</v>
+        <v>-34.97922592704563</v>
       </c>
       <c r="F24">
-        <v>-2.96784919860809</v>
+        <v>-3.940683048088426</v>
       </c>
       <c r="G24">
-        <v>-7.420766916376812</v>
+        <v>-10.90049909894637</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.251266248947333</v>
       </c>
       <c r="E25">
-        <v>-29.06976659989215</v>
+        <v>-34.63402261767792</v>
       </c>
       <c r="F25">
-        <v>-2.86158042960515</v>
+        <v>-4.529374768398937</v>
       </c>
       <c r="G25">
-        <v>-7.517270923661641</v>
+        <v>-10.47697870738261</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.515249096879748</v>
       </c>
       <c r="E26">
-        <v>-30.76241508600517</v>
+        <v>-35.9123700737772</v>
       </c>
       <c r="F26">
-        <v>-2.574435153098729</v>
+        <v>-4.367995544455148</v>
       </c>
       <c r="G26">
-        <v>-8.007731516259639</v>
+        <v>-10.62789193056615</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.757973644777988</v>
       </c>
       <c r="E27">
-        <v>-31.15686328596929</v>
+        <v>-35.5415514511851</v>
       </c>
       <c r="F27">
-        <v>-2.708748300523447</v>
+        <v>-3.776194961281931</v>
       </c>
       <c r="G27">
-        <v>-8.411512078921788</v>
+        <v>-11.32875101199886</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.964516396901636</v>
       </c>
       <c r="E28">
-        <v>-30.29889860047606</v>
+        <v>-35.75164094582295</v>
       </c>
       <c r="F28">
-        <v>-2.926674368484537</v>
+        <v>-4.263122574525926</v>
       </c>
       <c r="G28">
-        <v>-8.04519978524694</v>
+        <v>-12.26330525533835</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.113530715910796</v>
       </c>
       <c r="E29">
-        <v>-30.06714488618552</v>
+        <v>-35.4619091788122</v>
       </c>
       <c r="F29">
-        <v>-2.99563098456318</v>
+        <v>-3.999855816772603</v>
       </c>
       <c r="G29">
-        <v>-8.701535971339547</v>
+        <v>-12.1624175360501</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.203858498946676</v>
       </c>
       <c r="E30">
-        <v>-29.83757842484068</v>
+        <v>-33.33186897372033</v>
       </c>
       <c r="F30">
-        <v>-2.611946114199699</v>
+        <v>-3.813750654222652</v>
       </c>
       <c r="G30">
-        <v>-7.715243426450738</v>
+        <v>-11.58460754431812</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.222480704353186</v>
       </c>
       <c r="E31">
-        <v>-29.67505149270539</v>
+        <v>-34.85671938395313</v>
       </c>
       <c r="F31">
-        <v>-2.873478270611559</v>
+        <v>-4.183842015506193</v>
       </c>
       <c r="G31">
-        <v>-8.391988810643092</v>
+        <v>-11.5663967646632</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.179854263510082</v>
       </c>
       <c r="E32">
-        <v>-29.67883050426479</v>
+        <v>-34.19771773246091</v>
       </c>
       <c r="F32">
-        <v>-2.919852762922484</v>
+        <v>-4.384168589627406</v>
       </c>
       <c r="G32">
-        <v>-8.597937963043199</v>
+        <v>-10.72050769030303</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.077179711310727</v>
       </c>
       <c r="E33">
-        <v>-29.23422266195471</v>
+        <v>-36.21735826971979</v>
       </c>
       <c r="F33">
-        <v>-2.971196631282802</v>
+        <v>-3.930645720268705</v>
       </c>
       <c r="G33">
-        <v>-8.374542555611525</v>
+        <v>-11.09291977485689</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.930346564645728</v>
       </c>
       <c r="E34">
-        <v>-29.39372910192688</v>
+        <v>-34.57995716650034</v>
       </c>
       <c r="F34">
-        <v>-3.015112529142218</v>
+        <v>-4.203996194416305</v>
       </c>
       <c r="G34">
-        <v>-8.186587622243412</v>
+        <v>-11.26818950567619</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.752678375428382</v>
       </c>
       <c r="E35">
-        <v>-29.60765194981222</v>
+        <v>-35.11036147735975</v>
       </c>
       <c r="F35">
-        <v>-2.941517055607899</v>
+        <v>-4.354609127225909</v>
       </c>
       <c r="G35">
-        <v>-8.592012076906842</v>
+        <v>-11.14331933800996</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.559009490523645</v>
       </c>
       <c r="E36">
-        <v>-28.97974053661966</v>
+        <v>-32.93606449579091</v>
       </c>
       <c r="F36">
-        <v>-2.842503128318677</v>
+        <v>-4.747951933138628</v>
       </c>
       <c r="G36">
-        <v>-8.73413162631107</v>
+        <v>-11.02692456563178</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.368291022537519</v>
       </c>
       <c r="E37">
-        <v>-28.58217674653827</v>
+        <v>-34.60288030192717</v>
       </c>
       <c r="F37">
-        <v>-3.090337401357844</v>
+        <v>-3.94750465365048</v>
       </c>
       <c r="G37">
-        <v>-8.055647194692211</v>
+        <v>-11.91948245423193</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.187993181427418</v>
       </c>
       <c r="E38">
-        <v>-27.24038084111752</v>
+        <v>-32.45983658372227</v>
       </c>
       <c r="F38">
-        <v>-3.074539606619055</v>
+        <v>-4.554027810673653</v>
       </c>
       <c r="G38">
-        <v>-8.390508979719781</v>
+        <v>-11.13973952528861</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.039186945984491</v>
       </c>
       <c r="E39">
-        <v>-27.75049079571155</v>
+        <v>-32.90750567446154</v>
       </c>
       <c r="F39">
-        <v>-3.009400107532513</v>
+        <v>-4.767271946074121</v>
       </c>
       <c r="G39">
-        <v>-7.878008421906993</v>
+        <v>-11.1640205648285</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.921479798028687</v>
       </c>
       <c r="E40">
-        <v>-27.83276863995691</v>
+        <v>-32.25537824651296</v>
       </c>
       <c r="F40">
-        <v>-2.837045015501631</v>
+        <v>-4.316220096677971</v>
       </c>
       <c r="G40">
-        <v>-7.798153332814787</v>
+        <v>-11.31609534044408</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.852207185702038</v>
       </c>
       <c r="E41">
-        <v>-27.15501457759893</v>
+        <v>-31.25448586438964</v>
       </c>
       <c r="F41">
-        <v>-3.091954374528109</v>
+        <v>-4.524437698678252</v>
       </c>
       <c r="G41">
-        <v>-7.428786221868095</v>
+        <v>-12.15325308423457</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.827457374310655</v>
       </c>
       <c r="E42">
-        <v>-26.20166211560814</v>
+        <v>-31.07794556943762</v>
       </c>
       <c r="F42">
-        <v>-3.285021136731187</v>
+        <v>-4.254874520296251</v>
       </c>
       <c r="G42">
-        <v>-7.782150815269375</v>
+        <v>-10.39199835021455</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.855128254895805</v>
       </c>
       <c r="E43">
-        <v>-25.78426360937314</v>
+        <v>-31.78654759673585</v>
       </c>
       <c r="F43">
-        <v>-3.133310617112874</v>
+        <v>-4.921697854038811</v>
       </c>
       <c r="G43">
-        <v>-7.77886959370993</v>
+        <v>-11.41955225621337</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.932878933799027</v>
       </c>
       <c r="E44">
-        <v>-25.51622776133314</v>
+        <v>-28.19381934411447</v>
       </c>
       <c r="F44">
-        <v>-3.31915981413536</v>
+        <v>-5.537958469881892</v>
       </c>
       <c r="G44">
-        <v>-7.945312838534323</v>
+        <v>-11.12842259213008</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.057280827747565</v>
       </c>
       <c r="E45">
-        <v>-24.43594217290735</v>
+        <v>-32.32349781677334</v>
       </c>
       <c r="F45">
-        <v>-3.393720335693941</v>
+        <v>-4.442660440306482</v>
       </c>
       <c r="G45">
-        <v>-7.380949292752951</v>
+        <v>-10.60108106920393</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.227668292106115</v>
       </c>
       <c r="E46">
-        <v>-24.52598182160186</v>
+        <v>-30.12259378617243</v>
       </c>
       <c r="F46">
-        <v>-3.564341654750763</v>
+        <v>-5.156167247401211</v>
       </c>
       <c r="G46">
-        <v>-7.833748024291643</v>
+        <v>-10.26556303986446</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.428546211318657</v>
       </c>
       <c r="E47">
-        <v>-24.00477257721503</v>
+        <v>-30.54810278935517</v>
       </c>
       <c r="F47">
-        <v>-3.297966034134735</v>
+        <v>-4.61944978304455</v>
       </c>
       <c r="G47">
-        <v>-7.204347385980517</v>
+        <v>-11.39867712465219</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.659142931791114</v>
       </c>
       <c r="E48">
-        <v>-23.51745443230161</v>
+        <v>-29.46213623028675</v>
       </c>
       <c r="F48">
-        <v>-3.090589225048295</v>
+        <v>-4.589374247751108</v>
       </c>
       <c r="G48">
-        <v>-7.879944342627065</v>
+        <v>-11.3415477760807</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.896834335634016</v>
       </c>
       <c r="E49">
-        <v>-23.60220935182917</v>
+        <v>-29.77142194806262</v>
       </c>
       <c r="F49">
-        <v>-3.287316542804344</v>
+        <v>-5.099178883558216</v>
       </c>
       <c r="G49">
-        <v>-8.299711016726828</v>
+        <v>-10.75902923141092</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.141179682713492</v>
       </c>
       <c r="E50">
-        <v>-22.4716984581843</v>
+        <v>-27.91662239315695</v>
       </c>
       <c r="F50">
-        <v>-3.329849067101085</v>
+        <v>-4.277201506903906</v>
       </c>
       <c r="G50">
-        <v>-7.89291501145155</v>
+        <v>-9.935852772685221</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.374802298902955</v>
       </c>
       <c r="E51">
-        <v>-21.7469388356267</v>
+        <v>-28.61723619230565</v>
       </c>
       <c r="F51">
-        <v>-3.230080497107912</v>
+        <v>-5.096480890927298</v>
       </c>
       <c r="G51">
-        <v>-7.804272811023151</v>
+        <v>-10.45270094906427</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.596756924299711</v>
       </c>
       <c r="E52">
-        <v>-21.82364665684263</v>
+        <v>-28.28601454643663</v>
       </c>
       <c r="F52">
-        <v>-3.512226576338438</v>
+        <v>-4.163458378825506</v>
       </c>
       <c r="G52">
-        <v>-7.610716832453067</v>
+        <v>-10.93041071468227</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.802437446223163</v>
       </c>
       <c r="E53">
-        <v>-21.39231856456004</v>
+        <v>-26.47666275667194</v>
       </c>
       <c r="F53">
-        <v>-3.384776452845915</v>
+        <v>-4.488970319959988</v>
       </c>
       <c r="G53">
-        <v>-8.031638496541754</v>
+        <v>-11.46256578963614</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.990436629612773</v>
       </c>
       <c r="E54">
-        <v>-22.09566303353537</v>
+        <v>-26.66047351664328</v>
       </c>
       <c r="F54">
-        <v>-3.379775598835214</v>
+        <v>-5.107405400235418</v>
       </c>
       <c r="G54">
-        <v>-7.856109549219259</v>
+        <v>-10.60462150726657</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.167165856479453</v>
       </c>
       <c r="E55">
-        <v>-20.50971898046509</v>
+        <v>-25.67686179133323</v>
       </c>
       <c r="F55">
-        <v>-3.502128777698312</v>
+        <v>-4.806108295019571</v>
       </c>
       <c r="G55">
-        <v>-7.993267891625607</v>
+        <v>-11.2778166097316</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.327556044637493</v>
       </c>
       <c r="E56">
-        <v>-20.23933285441511</v>
+        <v>-26.53137577963261</v>
       </c>
       <c r="F56">
-        <v>-3.426925443035159</v>
+        <v>-4.691038950729289</v>
       </c>
       <c r="G56">
-        <v>-8.395680184897467</v>
+        <v>-11.29834721302905</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.484883654159907</v>
       </c>
       <c r="E57">
-        <v>-20.25666332444246</v>
+        <v>-24.690188817594</v>
       </c>
       <c r="F57">
-        <v>-3.432367816871551</v>
+        <v>-4.804828467382245</v>
       </c>
       <c r="G57">
-        <v>-8.521521594145291</v>
+        <v>-10.66982922331741</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.630104496861753</v>
       </c>
       <c r="E58">
-        <v>-19.74646280036828</v>
+        <v>-24.72022165721286</v>
       </c>
       <c r="F58">
-        <v>-3.29628693340926</v>
+        <v>-4.432748195964583</v>
       </c>
       <c r="G58">
-        <v>-8.818130898232855</v>
+        <v>-11.37618106964063</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.777038283498396</v>
       </c>
       <c r="E59">
-        <v>-18.98323831958952</v>
+        <v>-23.94089392286283</v>
       </c>
       <c r="F59">
-        <v>-3.463280003241821</v>
+        <v>-4.694782343022539</v>
       </c>
       <c r="G59">
-        <v>-8.442644309077799</v>
+        <v>-12.0895120742208</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.917319338146422</v>
       </c>
       <c r="E60">
-        <v>-19.33785859065618</v>
+        <v>-23.51579248234079</v>
       </c>
       <c r="F60">
-        <v>-3.327910687378534</v>
+        <v>-4.892153302250564</v>
       </c>
       <c r="G60">
-        <v>-8.149007791723092</v>
+        <v>-11.33505095739299</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.05755918609134</v>
       </c>
       <c r="E61">
-        <v>-18.82519457672183</v>
+        <v>-22.03393993281082</v>
       </c>
       <c r="F61">
-        <v>-3.767893063171075</v>
+        <v>-4.975501973585445</v>
       </c>
       <c r="G61">
-        <v>-8.446729429919309</v>
+        <v>-12.37653364891166</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.19279705835028</v>
       </c>
       <c r="E62">
-        <v>-17.85550790898537</v>
+        <v>-21.98463390781531</v>
       </c>
       <c r="F62">
-        <v>-3.540970096848178</v>
+        <v>-4.84944516406443</v>
       </c>
       <c r="G62">
-        <v>-8.988150674557042</v>
+        <v>-13.10841339896737</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.32028217192467</v>
       </c>
       <c r="E63">
-        <v>-17.3098901896972</v>
+        <v>-23.24366289379786</v>
       </c>
       <c r="F63">
-        <v>-3.569354934272506</v>
+        <v>-4.335379406337321</v>
       </c>
       <c r="G63">
-        <v>-9.023187558368793</v>
+        <v>-11.90469398866351</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.44107722587884</v>
       </c>
       <c r="E64">
-        <v>-18.15257127541454</v>
+        <v>-23.12787434189574</v>
       </c>
       <c r="F64">
-        <v>-3.555131865966438</v>
+        <v>-5.095555604538371</v>
       </c>
       <c r="G64">
-        <v>-8.995359518323143</v>
+        <v>-12.20924056770337</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.54476097253243</v>
       </c>
       <c r="E65">
-        <v>-17.12940332964749</v>
+        <v>-23.52660647827111</v>
       </c>
       <c r="F65">
-        <v>-3.994623848256522</v>
+        <v>-4.79720748727649</v>
       </c>
       <c r="G65">
-        <v>-9.248719041035667</v>
+        <v>-12.15912318960441</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.63970605153824</v>
       </c>
       <c r="E66">
-        <v>-17.13530845975349</v>
+        <v>-23.14518216955305</v>
       </c>
       <c r="F66">
-        <v>-3.946109682944166</v>
+        <v>-4.75209791198964</v>
       </c>
       <c r="G66">
-        <v>-9.243711896935954</v>
+        <v>-11.50521838868736</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.71206587477464</v>
       </c>
       <c r="E67">
-        <v>-17.61313039467283</v>
+        <v>-22.33263354988275</v>
       </c>
       <c r="F67">
-        <v>-3.70076713905262</v>
+        <v>-4.472664736003283</v>
       </c>
       <c r="G67">
-        <v>-9.50550744027781</v>
+        <v>-12.45455125393058</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.77465946550399</v>
       </c>
       <c r="E68">
-        <v>-17.21533565241704</v>
+        <v>-21.38735082857363</v>
       </c>
       <c r="F68">
-        <v>-3.944262423635923</v>
+        <v>-4.670488812200638</v>
       </c>
       <c r="G68">
-        <v>-9.204868796115248</v>
+        <v>-12.99208753224193</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.8165616734273</v>
       </c>
       <c r="E69">
-        <v>-17.27762934086655</v>
+        <v>-22.36875265856793</v>
       </c>
       <c r="F69">
-        <v>-3.938601360805191</v>
+        <v>-4.634776236731146</v>
       </c>
       <c r="G69">
-        <v>-9.325371657885855</v>
+        <v>-11.6259771857396</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.84687340683123</v>
       </c>
       <c r="E70">
-        <v>-16.39237607100311</v>
+        <v>-21.95703738721257</v>
       </c>
       <c r="F70">
-        <v>-3.667923199899022</v>
+        <v>-4.723273211474425</v>
       </c>
       <c r="G70">
-        <v>-9.056081804502226</v>
+        <v>-11.54928191300914</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.86043371976984</v>
       </c>
       <c r="E71">
-        <v>-16.67316863032271</v>
+        <v>-22.68322800755659</v>
       </c>
       <c r="F71">
-        <v>-4.190201392057485</v>
+        <v>-5.010779656168467</v>
       </c>
       <c r="G71">
-        <v>-8.823046168128903</v>
+        <v>-13.0130939126655</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.85822251724736</v>
       </c>
       <c r="E72">
-        <v>-16.10228202607174</v>
+        <v>-22.12873447921339</v>
       </c>
       <c r="F72">
-        <v>-4.080826245294046</v>
+        <v>-4.745831312587462</v>
       </c>
       <c r="G72">
-        <v>-9.284976539267531</v>
+        <v>-12.08653600626638</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.84250882718748</v>
       </c>
       <c r="E73">
-        <v>-17.05211586375858</v>
+        <v>-22.30645897011842</v>
       </c>
       <c r="F73">
-        <v>-3.993322483066724</v>
+        <v>-4.938991680307056</v>
       </c>
       <c r="G73">
-        <v>-8.620542298366214</v>
+        <v>-11.40001258182688</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.80690790735498</v>
       </c>
       <c r="E74">
-        <v>-16.69192556966249</v>
+        <v>-22.47269472246599</v>
       </c>
       <c r="F74">
-        <v>-4.336361850077041</v>
+        <v>-5.470514452680762</v>
       </c>
       <c r="G74">
-        <v>-8.686704849890857</v>
+        <v>-12.85356092044529</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.7601231263426</v>
       </c>
       <c r="E75">
-        <v>-15.97783956034096</v>
+        <v>-22.81618400442179</v>
       </c>
       <c r="F75">
-        <v>-4.350632963692471</v>
+        <v>-5.342381754448331</v>
       </c>
       <c r="G75">
-        <v>-9.036693066307468</v>
+        <v>-11.17519968668153</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.68950177405269</v>
       </c>
       <c r="E76">
-        <v>-17.23929127991762</v>
+        <v>-23.34709324013305</v>
       </c>
       <c r="F76">
-        <v>-4.257820194780606</v>
+        <v>-5.27279806424577</v>
       </c>
       <c r="G76">
-        <v>-8.609579737136109</v>
+        <v>-11.17216455673904</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.60701312260842</v>
       </c>
       <c r="E77">
-        <v>-17.31281558390615</v>
+        <v>-23.35004127671204</v>
       </c>
       <c r="F77">
-        <v>-4.09176649358282</v>
+        <v>-5.105227622333458</v>
       </c>
       <c r="G77">
-        <v>-8.260231358923589</v>
+        <v>-11.36844394920346</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.49878655940228</v>
       </c>
       <c r="E78">
-        <v>-18.45160905651105</v>
+        <v>-23.04344094402272</v>
       </c>
       <c r="F78">
-        <v>-4.304217881378809</v>
+        <v>-5.472042790538927</v>
       </c>
       <c r="G78">
-        <v>-8.415295327379827</v>
+        <v>-9.980858007594566</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.37328936274751</v>
       </c>
       <c r="E79">
-        <v>-18.23459552511547</v>
+        <v>-24.04422917124386</v>
       </c>
       <c r="F79">
-        <v>-4.276943884641635</v>
+        <v>-5.596235773403643</v>
       </c>
       <c r="G79">
-        <v>-8.147747802644265</v>
+        <v>-10.75046852436232</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.22320883323864</v>
       </c>
       <c r="E80">
-        <v>-19.06588297022951</v>
+        <v>-26.30650081735971</v>
       </c>
       <c r="F80">
-        <v>-4.54539539396908</v>
+        <v>-5.518693957562387</v>
       </c>
       <c r="G80">
-        <v>-8.321819887594366</v>
+        <v>-11.12921664774747</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.05177376023676</v>
       </c>
       <c r="E81">
-        <v>-19.27745780434187</v>
+        <v>-25.104050585629</v>
       </c>
       <c r="F81">
-        <v>-4.516221950777286</v>
+        <v>-5.138776502146838</v>
       </c>
       <c r="G81">
-        <v>-7.87572141048006</v>
+        <v>-10.47838307021005</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.861798044759801</v>
       </c>
       <c r="E82">
-        <v>-20.11849052552042</v>
+        <v>-25.46888709405696</v>
       </c>
       <c r="F82">
-        <v>-4.536656117869544</v>
+        <v>-6.052366343346357</v>
       </c>
       <c r="G82">
-        <v>-7.450688375777388</v>
+        <v>-9.401640371813587</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.652634778359076</v>
       </c>
       <c r="E83">
-        <v>-20.57547695153047</v>
+        <v>-25.81395681344144</v>
       </c>
       <c r="F83">
-        <v>-4.873349362207015</v>
+        <v>-5.797388229825446</v>
       </c>
       <c r="G83">
-        <v>-8.094569044830344</v>
+        <v>-11.53583874828009</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.437366919325903</v>
       </c>
       <c r="E84">
-        <v>-20.92665105387729</v>
+        <v>-26.90370238406926</v>
       </c>
       <c r="F84">
-        <v>-4.887839993184187</v>
+        <v>-5.579897883118228</v>
       </c>
       <c r="G84">
-        <v>-6.966951006154692</v>
+        <v>-10.06940177137618</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.211474423332811</v>
       </c>
       <c r="E85">
-        <v>-22.19478227261526</v>
+        <v>-28.27893201308863</v>
       </c>
       <c r="F85">
-        <v>-5.003648241197766</v>
+        <v>-5.776551476175428</v>
       </c>
       <c r="G85">
-        <v>-7.228001712202554</v>
+        <v>-10.39733033524865</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.996568568573052</v>
       </c>
       <c r="E86">
-        <v>-23.37332669005949</v>
+        <v>-28.57829584431369</v>
       </c>
       <c r="F86">
-        <v>-5.09379449544002</v>
+        <v>-6.388082942515926</v>
       </c>
       <c r="G86">
-        <v>-7.04779702415785</v>
+        <v>-9.15899731871421</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.789589537110688</v>
       </c>
       <c r="E87">
-        <v>-24.45083632391858</v>
+        <v>-28.40260463823811</v>
       </c>
       <c r="F87">
-        <v>-5.136227615648424</v>
+        <v>-6.25035816394278</v>
       </c>
       <c r="G87">
-        <v>-7.967277335653246</v>
+        <v>-10.22559119882731</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.610867185799107</v>
       </c>
       <c r="E88">
-        <v>-25.55816595911818</v>
+        <v>-30.69508799869613</v>
       </c>
       <c r="F88">
-        <v>-4.952368157127463</v>
+        <v>-6.212156758611576</v>
       </c>
       <c r="G88">
-        <v>-7.072081344919301</v>
+        <v>-9.59308324369939</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.463202741956646</v>
       </c>
       <c r="E89">
-        <v>-27.25801019042938</v>
+        <v>-31.44970837886031</v>
       </c>
       <c r="F89">
-        <v>-5.334773199853617</v>
+        <v>-6.142484433096915</v>
       </c>
       <c r="G89">
-        <v>-7.251098230759485</v>
+        <v>-10.25759295269657</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.359079299763861</v>
       </c>
       <c r="E90">
-        <v>-28.60411720310543</v>
+        <v>-34.14309075050638</v>
       </c>
       <c r="F90">
-        <v>-5.157867057311756</v>
+        <v>-6.316498330851903</v>
       </c>
       <c r="G90">
-        <v>-7.428362944286927</v>
+        <v>-9.639240187376098</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.308395775996965</v>
       </c>
       <c r="E91">
-        <v>-30.73566539004186</v>
+        <v>-34.50820123161181</v>
       </c>
       <c r="F91">
-        <v>-5.544224240916667</v>
+        <v>-6.397995601041527</v>
       </c>
       <c r="G91">
-        <v>-7.721996180420075</v>
+        <v>-10.41195802096065</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.313260928489312</v>
       </c>
       <c r="E92">
-        <v>-31.63622943052524</v>
+        <v>-36.3018550662289</v>
       </c>
       <c r="F92">
-        <v>-5.471981491351119</v>
+        <v>-6.735332486850973</v>
       </c>
       <c r="G92">
-        <v>-8.156075542962135</v>
+        <v>-10.98562054864149</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.388763078080682</v>
       </c>
       <c r="E93">
-        <v>-34.04558591241022</v>
+        <v>-38.01186572168734</v>
       </c>
       <c r="F93">
-        <v>-5.414079438262837</v>
+        <v>-6.196046669361931</v>
       </c>
       <c r="G93">
-        <v>-8.112458264772437</v>
+        <v>-11.51607923204912</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.524578586245262</v>
       </c>
       <c r="E94">
-        <v>-35.46091291453051</v>
+        <v>-39.28669455348265</v>
       </c>
       <c r="F94">
-        <v>-5.277219889441914</v>
+        <v>-6.390353497567</v>
       </c>
       <c r="G94">
-        <v>-8.071846585531189</v>
+        <v>-11.84618980825861</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.733970194843623</v>
       </c>
       <c r="E95">
-        <v>-37.73622203731445</v>
+        <v>-41.80489064390498</v>
       </c>
       <c r="F95">
-        <v>-5.449734028014134</v>
+        <v>-6.987983302153717</v>
       </c>
       <c r="G95">
-        <v>-9.208346890968258</v>
+        <v>-11.59347996741486</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.004918343336762</v>
       </c>
       <c r="E96">
-        <v>-39.09301398441159</v>
+        <v>-43.56089700985932</v>
       </c>
       <c r="F96">
-        <v>-5.283345666385616</v>
+        <v>-7.013185966200191</v>
       </c>
       <c r="G96">
-        <v>-9.341423393754658</v>
+        <v>-11.38229398540588</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.336742226925629</v>
       </c>
       <c r="E97">
-        <v>-41.84748773465813</v>
+        <v>-45.95332152742962</v>
       </c>
       <c r="F97">
-        <v>-5.298284444127702</v>
+        <v>-6.843200004941315</v>
       </c>
       <c r="G97">
-        <v>-9.065620315575533</v>
+        <v>-12.36879980969605</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.728854407567537</v>
       </c>
       <c r="E98">
-        <v>-43.90619088870718</v>
+        <v>-46.73398742584892</v>
       </c>
       <c r="F98">
-        <v>-5.61229947407873</v>
+        <v>-6.256599498139172</v>
       </c>
       <c r="G98">
-        <v>-9.645891223477092</v>
+        <v>-13.18323509418738</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.1574173858608</v>
       </c>
       <c r="E99">
-        <v>-46.47249295851299</v>
+        <v>-50.93754455558743</v>
       </c>
       <c r="F99">
-        <v>-5.334929761292747</v>
+        <v>-6.903836498826239</v>
       </c>
       <c r="G99">
-        <v>-9.917067779257401</v>
+        <v>-12.8828326979771</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.64483743523239</v>
       </c>
       <c r="E100">
-        <v>-47.95011591331981</v>
+        <v>-52.37528071133467</v>
       </c>
       <c r="F100">
-        <v>-5.125764506983663</v>
+        <v>-5.784039917496735</v>
       </c>
       <c r="G100">
-        <v>-10.681950055758</v>
+        <v>-12.87276919145429</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.12911127113724</v>
       </c>
       <c r="E101">
-        <v>-50.83022877855365</v>
+        <v>-54.62075511523757</v>
       </c>
       <c r="F101">
-        <v>-5.199388973377081</v>
+        <v>-6.279621484997776</v>
       </c>
       <c r="G101">
-        <v>-11.30732135399413</v>
+        <v>-14.29810886832615</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.6886668763648</v>
       </c>
       <c r="E102">
-        <v>-53.09340385523404</v>
+        <v>-55.1384774346385</v>
       </c>
       <c r="F102">
-        <v>-5.279472220410126</v>
+        <v>-6.709794334006364</v>
       </c>
       <c r="G102">
-        <v>-11.10700934023315</v>
+        <v>-15.51044968827745</v>
       </c>
     </row>
   </sheetData>
